--- a/lista_invitaciones_familias.xlsx
+++ b/lista_invitaciones_familias.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">Dirección de la tarjeta (pégala aquí):</t>
   </si>
   <si>
-    <t xml:space="preserve">https://TU-USUARIO.github.io/TU-REPO/</t>
+    <t xml:space="preserve">https://crubio29-cpu.github.io/boda-cristian-daniela/</t>
   </si>
   <si>
     <t xml:space="preserve">Familias registradas</t>
@@ -50,10 +50,10 @@
     <t xml:space="preserve">Tope de personas</t>
   </si>
   <si>
-    <t xml:space="preserve">Enlace de la tarjeta (se genera solo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mensaje para WhatsApp (se genera solo)</t>
+    <t xml:space="preserve">Mensaje 1 · solo el enlace (envíalo primero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mensaje 2 · texto sin enlace (envíalo después)</t>
   </si>
   <si>
     <t xml:space="preserve">Teléfono (opcional)</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">Cómo usar esta hoja</t>
   </si>
   <si>
-    <t xml:space="preserve">Cuando publiques la tarjeta, pega su dirección en la celda amarilla de arriba (hoja Invitaciones, B1). Debe terminar en /.</t>
+    <t xml:space="preserve">La dirección de tu tarjeta ya está cargada en la celda amarilla B1 (hoja Invitaciones). Cámbiala solo si algún día cambia el enlace; debe terminar en /.</t>
   </si>
   <si>
     <t xml:space="preserve">Escribe cada familia en la columna A, con el nombre IDÉNTICO a la opción del formulario (tildes y mayúsculas incluidas).</t>
@@ -86,22 +86,22 @@
     <t xml:space="preserve">En la columna B escribe el tope de personas de esa familia (adultos y niños). Es solo informativo: el formulario es quien lo hace cumplir.</t>
   </si>
   <si>
-    <t xml:space="preserve">La columna C genera el enlace de la tarjeta de esa familia. Ese es el enlace que se envía (no el del formulario).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La columna D genera un mensaje listo para WhatsApp. Haz clic en la celda, copia (Ctrl+C) y pega en el chat.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marca "Sí" en la columna F cuando envíes cada invitación: la fila se pinta de verde y se actualiza el contador de arriba.</t>
+    <t xml:space="preserve">Por WhatsApp se envían DOS mensajes a cada familia. Primero el Mensaje 1 (columna C): es solo el enlace, y WhatsApp muestra la vista previa con la imagen. No le agregues texto ni foto, o la vista previa desaparece.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Después envía el Mensaje 2 (columna D): es el texto cordial para esa familia, sin enlace. Haz clic en la celda, copia (Ctrl+C) y pega en el chat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marca "Sí" en la columna F cuando envíes los dos mensajes: la fila se pinta de verde y se actualiza el contador de arriba.</t>
   </si>
   <si>
     <t xml:space="preserve">Si dos familias tienen el mismo nombre, la celda se pinta de rojo: cambia uno, o el formulario no sabrá cuál es cuál.</t>
   </si>
   <si>
-    <t xml:space="preserve">Antes de enviar a todos, abre 2 o 3 enlaces desde tu celular y confirma que el saludo, el tope y el formulario salen bien.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Para recordatorios: reenvía el mismo enlace de la tarjeta. Cierra el formulario después del 1 de diciembre de 2026.</t>
+    <t xml:space="preserve">Antes de enviar a todos, mándate a ti mismo los dos mensajes de una familia y comprueba que la vista previa, el saludo y el formulario salen bien.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para recordatorios: reenvía el mismo enlace de la tarjeta. Cierra el formulario (Aceptando respuestas) después del 1 de diciembre de 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Supuestos: el máximo de 80 familias (filas 5 a 84) y el tope de 1 a 30 personas son límites de esta plantilla; las fechas del mensaje (boda 23/12/2026 y confirmación antes del 1/12/2026) vienen de los datos que diste. La fila de ejemplo es solo una guía: bórrala.</t>
@@ -691,11 +691,11 @@
       </c>
       <c r="C5" s="9" t="str">
         <f aca="false">IF(A5="","",IF(RIGHT($B$1,1)="/",$B$1,$B$1&amp;"/")&amp;"?familia="&amp;H5&amp;IF(B5="","","&amp;max="&amp;B5))</f>
-        <v>https://TU-USUARIO.github.io/TU-REPO/?familia=Familia%20Ejemplo%20Uno&amp;max=4</v>
+        <v>https://crubio29-cpu.github.io/boda-cristian-daniela/?familia=Familia%20Ejemplo%20Uno&amp;max=4</v>
       </c>
       <c r="D5" s="9" t="str">
-        <f aca="false">IF(A5="","","Hola, "&amp;TRIM(A5)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B5="",""," (hasta "&amp;B5&amp;IF(B5=1," persona)"," personas)"))&amp;": "&amp;C5&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
-        <v>Hola, Familia Ejemplo Uno. Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada (hasta 4 personas): https://TU-USUARIO.github.io/TU-REPO/?familia=Familia%20Ejemplo%20Uno&amp;max=4  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!</v>
+        <f aca="false">IF(A5="","","Hola, "&amp;TRIM(A5)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B5="",""," (hasta "&amp;B5&amp;IF(B5=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
+        <v>Hola, Familia Ejemplo Uno 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 En el enlace que les acabamos de enviar está su invitación personalizada (hasta 4 personas) ✨ Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 ¡Los esperamos con mucho cariño! 🤍</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
@@ -715,7 +715,7 @@
         <v/>
       </c>
       <c r="D6" s="9" t="str">
-        <f aca="false">IF(A6="","","Hola, "&amp;TRIM(A6)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B6="",""," (hasta "&amp;B6&amp;IF(B6=1," persona)"," personas)"))&amp;": "&amp;C6&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A6="","","Hola, "&amp;TRIM(A6)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B6="",""," (hasta "&amp;B6&amp;IF(B6=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E6" s="7"/>
@@ -734,7 +734,7 @@
         <v/>
       </c>
       <c r="D7" s="9" t="str">
-        <f aca="false">IF(A7="","","Hola, "&amp;TRIM(A7)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B7="",""," (hasta "&amp;B7&amp;IF(B7=1," persona)"," personas)"))&amp;": "&amp;C7&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A7="","","Hola, "&amp;TRIM(A7)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B7="",""," (hasta "&amp;B7&amp;IF(B7=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E7" s="7"/>
@@ -753,7 +753,7 @@
         <v/>
       </c>
       <c r="D8" s="9" t="str">
-        <f aca="false">IF(A8="","","Hola, "&amp;TRIM(A8)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B8="",""," (hasta "&amp;B8&amp;IF(B8=1," persona)"," personas)"))&amp;": "&amp;C8&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A8="","","Hola, "&amp;TRIM(A8)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B8="",""," (hasta "&amp;B8&amp;IF(B8=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E8" s="7"/>
@@ -772,7 +772,7 @@
         <v/>
       </c>
       <c r="D9" s="9" t="str">
-        <f aca="false">IF(A9="","","Hola, "&amp;TRIM(A9)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B9="",""," (hasta "&amp;B9&amp;IF(B9=1," persona)"," personas)"))&amp;": "&amp;C9&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A9="","","Hola, "&amp;TRIM(A9)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B9="",""," (hasta "&amp;B9&amp;IF(B9=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E9" s="7"/>
@@ -791,7 +791,7 @@
         <v/>
       </c>
       <c r="D10" s="9" t="str">
-        <f aca="false">IF(A10="","","Hola, "&amp;TRIM(A10)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B10="",""," (hasta "&amp;B10&amp;IF(B10=1," persona)"," personas)"))&amp;": "&amp;C10&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A10="","","Hola, "&amp;TRIM(A10)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B10="",""," (hasta "&amp;B10&amp;IF(B10=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E10" s="7"/>
@@ -810,7 +810,7 @@
         <v/>
       </c>
       <c r="D11" s="9" t="str">
-        <f aca="false">IF(A11="","","Hola, "&amp;TRIM(A11)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B11="",""," (hasta "&amp;B11&amp;IF(B11=1," persona)"," personas)"))&amp;": "&amp;C11&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A11="","","Hola, "&amp;TRIM(A11)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B11="",""," (hasta "&amp;B11&amp;IF(B11=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E11" s="7"/>
@@ -829,7 +829,7 @@
         <v/>
       </c>
       <c r="D12" s="9" t="str">
-        <f aca="false">IF(A12="","","Hola, "&amp;TRIM(A12)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B12="",""," (hasta "&amp;B12&amp;IF(B12=1," persona)"," personas)"))&amp;": "&amp;C12&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A12="","","Hola, "&amp;TRIM(A12)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B12="",""," (hasta "&amp;B12&amp;IF(B12=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E12" s="7"/>
@@ -848,7 +848,7 @@
         <v/>
       </c>
       <c r="D13" s="9" t="str">
-        <f aca="false">IF(A13="","","Hola, "&amp;TRIM(A13)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B13="",""," (hasta "&amp;B13&amp;IF(B13=1," persona)"," personas)"))&amp;": "&amp;C13&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A13="","","Hola, "&amp;TRIM(A13)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B13="",""," (hasta "&amp;B13&amp;IF(B13=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E13" s="7"/>
@@ -867,7 +867,7 @@
         <v/>
       </c>
       <c r="D14" s="9" t="str">
-        <f aca="false">IF(A14="","","Hola, "&amp;TRIM(A14)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B14="",""," (hasta "&amp;B14&amp;IF(B14=1," persona)"," personas)"))&amp;": "&amp;C14&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A14="","","Hola, "&amp;TRIM(A14)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B14="",""," (hasta "&amp;B14&amp;IF(B14=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E14" s="7"/>
@@ -886,7 +886,7 @@
         <v/>
       </c>
       <c r="D15" s="9" t="str">
-        <f aca="false">IF(A15="","","Hola, "&amp;TRIM(A15)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B15="",""," (hasta "&amp;B15&amp;IF(B15=1," persona)"," personas)"))&amp;": "&amp;C15&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A15="","","Hola, "&amp;TRIM(A15)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B15="",""," (hasta "&amp;B15&amp;IF(B15=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E15" s="7"/>
@@ -905,7 +905,7 @@
         <v/>
       </c>
       <c r="D16" s="9" t="str">
-        <f aca="false">IF(A16="","","Hola, "&amp;TRIM(A16)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B16="",""," (hasta "&amp;B16&amp;IF(B16=1," persona)"," personas)"))&amp;": "&amp;C16&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A16="","","Hola, "&amp;TRIM(A16)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B16="",""," (hasta "&amp;B16&amp;IF(B16=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E16" s="7"/>
@@ -924,7 +924,7 @@
         <v/>
       </c>
       <c r="D17" s="9" t="str">
-        <f aca="false">IF(A17="","","Hola, "&amp;TRIM(A17)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B17="",""," (hasta "&amp;B17&amp;IF(B17=1," persona)"," personas)"))&amp;": "&amp;C17&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A17="","","Hola, "&amp;TRIM(A17)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B17="",""," (hasta "&amp;B17&amp;IF(B17=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E17" s="7"/>
@@ -943,7 +943,7 @@
         <v/>
       </c>
       <c r="D18" s="9" t="str">
-        <f aca="false">IF(A18="","","Hola, "&amp;TRIM(A18)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B18="",""," (hasta "&amp;B18&amp;IF(B18=1," persona)"," personas)"))&amp;": "&amp;C18&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A18="","","Hola, "&amp;TRIM(A18)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B18="",""," (hasta "&amp;B18&amp;IF(B18=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E18" s="7"/>
@@ -962,7 +962,7 @@
         <v/>
       </c>
       <c r="D19" s="9" t="str">
-        <f aca="false">IF(A19="","","Hola, "&amp;TRIM(A19)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B19="",""," (hasta "&amp;B19&amp;IF(B19=1," persona)"," personas)"))&amp;": "&amp;C19&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A19="","","Hola, "&amp;TRIM(A19)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B19="",""," (hasta "&amp;B19&amp;IF(B19=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E19" s="7"/>
@@ -981,7 +981,7 @@
         <v/>
       </c>
       <c r="D20" s="9" t="str">
-        <f aca="false">IF(A20="","","Hola, "&amp;TRIM(A20)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B20="",""," (hasta "&amp;B20&amp;IF(B20=1," persona)"," personas)"))&amp;": "&amp;C20&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A20="","","Hola, "&amp;TRIM(A20)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B20="",""," (hasta "&amp;B20&amp;IF(B20=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E20" s="7"/>
@@ -1000,7 +1000,7 @@
         <v/>
       </c>
       <c r="D21" s="9" t="str">
-        <f aca="false">IF(A21="","","Hola, "&amp;TRIM(A21)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B21="",""," (hasta "&amp;B21&amp;IF(B21=1," persona)"," personas)"))&amp;": "&amp;C21&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A21="","","Hola, "&amp;TRIM(A21)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B21="",""," (hasta "&amp;B21&amp;IF(B21=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E21" s="7"/>
@@ -1019,7 +1019,7 @@
         <v/>
       </c>
       <c r="D22" s="9" t="str">
-        <f aca="false">IF(A22="","","Hola, "&amp;TRIM(A22)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B22="",""," (hasta "&amp;B22&amp;IF(B22=1," persona)"," personas)"))&amp;": "&amp;C22&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A22="","","Hola, "&amp;TRIM(A22)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B22="",""," (hasta "&amp;B22&amp;IF(B22=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E22" s="7"/>
@@ -1038,7 +1038,7 @@
         <v/>
       </c>
       <c r="D23" s="9" t="str">
-        <f aca="false">IF(A23="","","Hola, "&amp;TRIM(A23)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B23="",""," (hasta "&amp;B23&amp;IF(B23=1," persona)"," personas)"))&amp;": "&amp;C23&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A23="","","Hola, "&amp;TRIM(A23)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B23="",""," (hasta "&amp;B23&amp;IF(B23=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E23" s="7"/>
@@ -1057,7 +1057,7 @@
         <v/>
       </c>
       <c r="D24" s="9" t="str">
-        <f aca="false">IF(A24="","","Hola, "&amp;TRIM(A24)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B24="",""," (hasta "&amp;B24&amp;IF(B24=1," persona)"," personas)"))&amp;": "&amp;C24&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A24="","","Hola, "&amp;TRIM(A24)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B24="",""," (hasta "&amp;B24&amp;IF(B24=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E24" s="7"/>
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="D25" s="9" t="str">
-        <f aca="false">IF(A25="","","Hola, "&amp;TRIM(A25)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B25="",""," (hasta "&amp;B25&amp;IF(B25=1," persona)"," personas)"))&amp;": "&amp;C25&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A25="","","Hola, "&amp;TRIM(A25)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B25="",""," (hasta "&amp;B25&amp;IF(B25=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E25" s="7"/>
@@ -1095,7 +1095,7 @@
         <v/>
       </c>
       <c r="D26" s="9" t="str">
-        <f aca="false">IF(A26="","","Hola, "&amp;TRIM(A26)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B26="",""," (hasta "&amp;B26&amp;IF(B26=1," persona)"," personas)"))&amp;": "&amp;C26&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A26="","","Hola, "&amp;TRIM(A26)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B26="",""," (hasta "&amp;B26&amp;IF(B26=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E26" s="7"/>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="D27" s="9" t="str">
-        <f aca="false">IF(A27="","","Hola, "&amp;TRIM(A27)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B27="",""," (hasta "&amp;B27&amp;IF(B27=1," persona)"," personas)"))&amp;": "&amp;C27&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A27="","","Hola, "&amp;TRIM(A27)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B27="",""," (hasta "&amp;B27&amp;IF(B27=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E27" s="7"/>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="D28" s="9" t="str">
-        <f aca="false">IF(A28="","","Hola, "&amp;TRIM(A28)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B28="",""," (hasta "&amp;B28&amp;IF(B28=1," persona)"," personas)"))&amp;": "&amp;C28&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A28="","","Hola, "&amp;TRIM(A28)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B28="",""," (hasta "&amp;B28&amp;IF(B28=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E28" s="7"/>
@@ -1152,7 +1152,7 @@
         <v/>
       </c>
       <c r="D29" s="9" t="str">
-        <f aca="false">IF(A29="","","Hola, "&amp;TRIM(A29)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B29="",""," (hasta "&amp;B29&amp;IF(B29=1," persona)"," personas)"))&amp;": "&amp;C29&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A29="","","Hola, "&amp;TRIM(A29)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B29="",""," (hasta "&amp;B29&amp;IF(B29=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E29" s="7"/>
@@ -1171,7 +1171,7 @@
         <v/>
       </c>
       <c r="D30" s="9" t="str">
-        <f aca="false">IF(A30="","","Hola, "&amp;TRIM(A30)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B30="",""," (hasta "&amp;B30&amp;IF(B30=1," persona)"," personas)"))&amp;": "&amp;C30&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A30="","","Hola, "&amp;TRIM(A30)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B30="",""," (hasta "&amp;B30&amp;IF(B30=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E30" s="7"/>
@@ -1190,7 +1190,7 @@
         <v/>
       </c>
       <c r="D31" s="9" t="str">
-        <f aca="false">IF(A31="","","Hola, "&amp;TRIM(A31)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B31="",""," (hasta "&amp;B31&amp;IF(B31=1," persona)"," personas)"))&amp;": "&amp;C31&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A31="","","Hola, "&amp;TRIM(A31)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B31="",""," (hasta "&amp;B31&amp;IF(B31=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E31" s="7"/>
@@ -1209,7 +1209,7 @@
         <v/>
       </c>
       <c r="D32" s="9" t="str">
-        <f aca="false">IF(A32="","","Hola, "&amp;TRIM(A32)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B32="",""," (hasta "&amp;B32&amp;IF(B32=1," persona)"," personas)"))&amp;": "&amp;C32&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A32="","","Hola, "&amp;TRIM(A32)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B32="",""," (hasta "&amp;B32&amp;IF(B32=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E32" s="7"/>
@@ -1228,7 +1228,7 @@
         <v/>
       </c>
       <c r="D33" s="9" t="str">
-        <f aca="false">IF(A33="","","Hola, "&amp;TRIM(A33)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B33="",""," (hasta "&amp;B33&amp;IF(B33=1," persona)"," personas)"))&amp;": "&amp;C33&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A33="","","Hola, "&amp;TRIM(A33)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B33="",""," (hasta "&amp;B33&amp;IF(B33=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E33" s="7"/>
@@ -1247,7 +1247,7 @@
         <v/>
       </c>
       <c r="D34" s="9" t="str">
-        <f aca="false">IF(A34="","","Hola, "&amp;TRIM(A34)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B34="",""," (hasta "&amp;B34&amp;IF(B34=1," persona)"," personas)"))&amp;": "&amp;C34&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A34="","","Hola, "&amp;TRIM(A34)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B34="",""," (hasta "&amp;B34&amp;IF(B34=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E34" s="7"/>
@@ -1266,7 +1266,7 @@
         <v/>
       </c>
       <c r="D35" s="9" t="str">
-        <f aca="false">IF(A35="","","Hola, "&amp;TRIM(A35)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B35="",""," (hasta "&amp;B35&amp;IF(B35=1," persona)"," personas)"))&amp;": "&amp;C35&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A35="","","Hola, "&amp;TRIM(A35)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B35="",""," (hasta "&amp;B35&amp;IF(B35=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E35" s="7"/>
@@ -1285,7 +1285,7 @@
         <v/>
       </c>
       <c r="D36" s="9" t="str">
-        <f aca="false">IF(A36="","","Hola, "&amp;TRIM(A36)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B36="",""," (hasta "&amp;B36&amp;IF(B36=1," persona)"," personas)"))&amp;": "&amp;C36&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A36="","","Hola, "&amp;TRIM(A36)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B36="",""," (hasta "&amp;B36&amp;IF(B36=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E36" s="7"/>
@@ -1304,7 +1304,7 @@
         <v/>
       </c>
       <c r="D37" s="9" t="str">
-        <f aca="false">IF(A37="","","Hola, "&amp;TRIM(A37)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B37="",""," (hasta "&amp;B37&amp;IF(B37=1," persona)"," personas)"))&amp;": "&amp;C37&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A37="","","Hola, "&amp;TRIM(A37)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B37="",""," (hasta "&amp;B37&amp;IF(B37=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E37" s="7"/>
@@ -1323,7 +1323,7 @@
         <v/>
       </c>
       <c r="D38" s="9" t="str">
-        <f aca="false">IF(A38="","","Hola, "&amp;TRIM(A38)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B38="",""," (hasta "&amp;B38&amp;IF(B38=1," persona)"," personas)"))&amp;": "&amp;C38&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A38="","","Hola, "&amp;TRIM(A38)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B38="",""," (hasta "&amp;B38&amp;IF(B38=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E38" s="7"/>
@@ -1342,7 +1342,7 @@
         <v/>
       </c>
       <c r="D39" s="9" t="str">
-        <f aca="false">IF(A39="","","Hola, "&amp;TRIM(A39)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B39="",""," (hasta "&amp;B39&amp;IF(B39=1," persona)"," personas)"))&amp;": "&amp;C39&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A39="","","Hola, "&amp;TRIM(A39)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B39="",""," (hasta "&amp;B39&amp;IF(B39=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E39" s="7"/>
@@ -1361,7 +1361,7 @@
         <v/>
       </c>
       <c r="D40" s="9" t="str">
-        <f aca="false">IF(A40="","","Hola, "&amp;TRIM(A40)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B40="",""," (hasta "&amp;B40&amp;IF(B40=1," persona)"," personas)"))&amp;": "&amp;C40&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A40="","","Hola, "&amp;TRIM(A40)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B40="",""," (hasta "&amp;B40&amp;IF(B40=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E40" s="7"/>
@@ -1380,7 +1380,7 @@
         <v/>
       </c>
       <c r="D41" s="9" t="str">
-        <f aca="false">IF(A41="","","Hola, "&amp;TRIM(A41)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B41="",""," (hasta "&amp;B41&amp;IF(B41=1," persona)"," personas)"))&amp;": "&amp;C41&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A41="","","Hola, "&amp;TRIM(A41)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B41="",""," (hasta "&amp;B41&amp;IF(B41=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E41" s="7"/>
@@ -1399,7 +1399,7 @@
         <v/>
       </c>
       <c r="D42" s="9" t="str">
-        <f aca="false">IF(A42="","","Hola, "&amp;TRIM(A42)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B42="",""," (hasta "&amp;B42&amp;IF(B42=1," persona)"," personas)"))&amp;": "&amp;C42&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A42="","","Hola, "&amp;TRIM(A42)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B42="",""," (hasta "&amp;B42&amp;IF(B42=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E42" s="7"/>
@@ -1418,7 +1418,7 @@
         <v/>
       </c>
       <c r="D43" s="9" t="str">
-        <f aca="false">IF(A43="","","Hola, "&amp;TRIM(A43)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B43="",""," (hasta "&amp;B43&amp;IF(B43=1," persona)"," personas)"))&amp;": "&amp;C43&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A43="","","Hola, "&amp;TRIM(A43)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B43="",""," (hasta "&amp;B43&amp;IF(B43=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E43" s="7"/>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="D44" s="9" t="str">
-        <f aca="false">IF(A44="","","Hola, "&amp;TRIM(A44)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B44="",""," (hasta "&amp;B44&amp;IF(B44=1," persona)"," personas)"))&amp;": "&amp;C44&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A44="","","Hola, "&amp;TRIM(A44)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B44="",""," (hasta "&amp;B44&amp;IF(B44=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E44" s="7"/>
@@ -1456,7 +1456,7 @@
         <v/>
       </c>
       <c r="D45" s="9" t="str">
-        <f aca="false">IF(A45="","","Hola, "&amp;TRIM(A45)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B45="",""," (hasta "&amp;B45&amp;IF(B45=1," persona)"," personas)"))&amp;": "&amp;C45&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A45="","","Hola, "&amp;TRIM(A45)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B45="",""," (hasta "&amp;B45&amp;IF(B45=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E45" s="7"/>
@@ -1475,7 +1475,7 @@
         <v/>
       </c>
       <c r="D46" s="9" t="str">
-        <f aca="false">IF(A46="","","Hola, "&amp;TRIM(A46)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B46="",""," (hasta "&amp;B46&amp;IF(B46=1," persona)"," personas)"))&amp;": "&amp;C46&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A46="","","Hola, "&amp;TRIM(A46)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B46="",""," (hasta "&amp;B46&amp;IF(B46=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E46" s="7"/>
@@ -1494,7 +1494,7 @@
         <v/>
       </c>
       <c r="D47" s="9" t="str">
-        <f aca="false">IF(A47="","","Hola, "&amp;TRIM(A47)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B47="",""," (hasta "&amp;B47&amp;IF(B47=1," persona)"," personas)"))&amp;": "&amp;C47&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A47="","","Hola, "&amp;TRIM(A47)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B47="",""," (hasta "&amp;B47&amp;IF(B47=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E47" s="7"/>
@@ -1513,7 +1513,7 @@
         <v/>
       </c>
       <c r="D48" s="9" t="str">
-        <f aca="false">IF(A48="","","Hola, "&amp;TRIM(A48)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B48="",""," (hasta "&amp;B48&amp;IF(B48=1," persona)"," personas)"))&amp;": "&amp;C48&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A48="","","Hola, "&amp;TRIM(A48)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B48="",""," (hasta "&amp;B48&amp;IF(B48=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E48" s="7"/>
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="D49" s="9" t="str">
-        <f aca="false">IF(A49="","","Hola, "&amp;TRIM(A49)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B49="",""," (hasta "&amp;B49&amp;IF(B49=1," persona)"," personas)"))&amp;": "&amp;C49&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A49="","","Hola, "&amp;TRIM(A49)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B49="",""," (hasta "&amp;B49&amp;IF(B49=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E49" s="7"/>
@@ -1551,7 +1551,7 @@
         <v/>
       </c>
       <c r="D50" s="9" t="str">
-        <f aca="false">IF(A50="","","Hola, "&amp;TRIM(A50)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B50="",""," (hasta "&amp;B50&amp;IF(B50=1," persona)"," personas)"))&amp;": "&amp;C50&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A50="","","Hola, "&amp;TRIM(A50)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B50="",""," (hasta "&amp;B50&amp;IF(B50=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E50" s="7"/>
@@ -1570,7 +1570,7 @@
         <v/>
       </c>
       <c r="D51" s="9" t="str">
-        <f aca="false">IF(A51="","","Hola, "&amp;TRIM(A51)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B51="",""," (hasta "&amp;B51&amp;IF(B51=1," persona)"," personas)"))&amp;": "&amp;C51&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A51="","","Hola, "&amp;TRIM(A51)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B51="",""," (hasta "&amp;B51&amp;IF(B51=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E51" s="7"/>
@@ -1589,7 +1589,7 @@
         <v/>
       </c>
       <c r="D52" s="9" t="str">
-        <f aca="false">IF(A52="","","Hola, "&amp;TRIM(A52)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B52="",""," (hasta "&amp;B52&amp;IF(B52=1," persona)"," personas)"))&amp;": "&amp;C52&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A52="","","Hola, "&amp;TRIM(A52)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B52="",""," (hasta "&amp;B52&amp;IF(B52=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E52" s="7"/>
@@ -1608,7 +1608,7 @@
         <v/>
       </c>
       <c r="D53" s="9" t="str">
-        <f aca="false">IF(A53="","","Hola, "&amp;TRIM(A53)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B53="",""," (hasta "&amp;B53&amp;IF(B53=1," persona)"," personas)"))&amp;": "&amp;C53&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A53="","","Hola, "&amp;TRIM(A53)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B53="",""," (hasta "&amp;B53&amp;IF(B53=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E53" s="7"/>
@@ -1627,7 +1627,7 @@
         <v/>
       </c>
       <c r="D54" s="9" t="str">
-        <f aca="false">IF(A54="","","Hola, "&amp;TRIM(A54)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B54="",""," (hasta "&amp;B54&amp;IF(B54=1," persona)"," personas)"))&amp;": "&amp;C54&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A54="","","Hola, "&amp;TRIM(A54)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B54="",""," (hasta "&amp;B54&amp;IF(B54=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E54" s="7"/>
@@ -1646,7 +1646,7 @@
         <v/>
       </c>
       <c r="D55" s="9" t="str">
-        <f aca="false">IF(A55="","","Hola, "&amp;TRIM(A55)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B55="",""," (hasta "&amp;B55&amp;IF(B55=1," persona)"," personas)"))&amp;": "&amp;C55&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A55="","","Hola, "&amp;TRIM(A55)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B55="",""," (hasta "&amp;B55&amp;IF(B55=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E55" s="7"/>
@@ -1665,7 +1665,7 @@
         <v/>
       </c>
       <c r="D56" s="9" t="str">
-        <f aca="false">IF(A56="","","Hola, "&amp;TRIM(A56)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B56="",""," (hasta "&amp;B56&amp;IF(B56=1," persona)"," personas)"))&amp;": "&amp;C56&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A56="","","Hola, "&amp;TRIM(A56)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B56="",""," (hasta "&amp;B56&amp;IF(B56=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E56" s="7"/>
@@ -1684,7 +1684,7 @@
         <v/>
       </c>
       <c r="D57" s="9" t="str">
-        <f aca="false">IF(A57="","","Hola, "&amp;TRIM(A57)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B57="",""," (hasta "&amp;B57&amp;IF(B57=1," persona)"," personas)"))&amp;": "&amp;C57&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A57="","","Hola, "&amp;TRIM(A57)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B57="",""," (hasta "&amp;B57&amp;IF(B57=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E57" s="7"/>
@@ -1703,7 +1703,7 @@
         <v/>
       </c>
       <c r="D58" s="9" t="str">
-        <f aca="false">IF(A58="","","Hola, "&amp;TRIM(A58)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B58="",""," (hasta "&amp;B58&amp;IF(B58=1," persona)"," personas)"))&amp;": "&amp;C58&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A58="","","Hola, "&amp;TRIM(A58)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B58="",""," (hasta "&amp;B58&amp;IF(B58=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E58" s="7"/>
@@ -1722,7 +1722,7 @@
         <v/>
       </c>
       <c r="D59" s="9" t="str">
-        <f aca="false">IF(A59="","","Hola, "&amp;TRIM(A59)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B59="",""," (hasta "&amp;B59&amp;IF(B59=1," persona)"," personas)"))&amp;": "&amp;C59&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A59="","","Hola, "&amp;TRIM(A59)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B59="",""," (hasta "&amp;B59&amp;IF(B59=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E59" s="7"/>
@@ -1741,7 +1741,7 @@
         <v/>
       </c>
       <c r="D60" s="9" t="str">
-        <f aca="false">IF(A60="","","Hola, "&amp;TRIM(A60)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B60="",""," (hasta "&amp;B60&amp;IF(B60=1," persona)"," personas)"))&amp;": "&amp;C60&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A60="","","Hola, "&amp;TRIM(A60)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B60="",""," (hasta "&amp;B60&amp;IF(B60=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E60" s="7"/>
@@ -1760,7 +1760,7 @@
         <v/>
       </c>
       <c r="D61" s="9" t="str">
-        <f aca="false">IF(A61="","","Hola, "&amp;TRIM(A61)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B61="",""," (hasta "&amp;B61&amp;IF(B61=1," persona)"," personas)"))&amp;": "&amp;C61&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A61="","","Hola, "&amp;TRIM(A61)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B61="",""," (hasta "&amp;B61&amp;IF(B61=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E61" s="7"/>
@@ -1779,7 +1779,7 @@
         <v/>
       </c>
       <c r="D62" s="9" t="str">
-        <f aca="false">IF(A62="","","Hola, "&amp;TRIM(A62)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B62="",""," (hasta "&amp;B62&amp;IF(B62=1," persona)"," personas)"))&amp;": "&amp;C62&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A62="","","Hola, "&amp;TRIM(A62)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B62="",""," (hasta "&amp;B62&amp;IF(B62=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E62" s="7"/>
@@ -1798,7 +1798,7 @@
         <v/>
       </c>
       <c r="D63" s="9" t="str">
-        <f aca="false">IF(A63="","","Hola, "&amp;TRIM(A63)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B63="",""," (hasta "&amp;B63&amp;IF(B63=1," persona)"," personas)"))&amp;": "&amp;C63&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A63="","","Hola, "&amp;TRIM(A63)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B63="",""," (hasta "&amp;B63&amp;IF(B63=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E63" s="7"/>
@@ -1817,7 +1817,7 @@
         <v/>
       </c>
       <c r="D64" s="9" t="str">
-        <f aca="false">IF(A64="","","Hola, "&amp;TRIM(A64)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B64="",""," (hasta "&amp;B64&amp;IF(B64=1," persona)"," personas)"))&amp;": "&amp;C64&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A64="","","Hola, "&amp;TRIM(A64)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B64="",""," (hasta "&amp;B64&amp;IF(B64=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E64" s="7"/>
@@ -1836,7 +1836,7 @@
         <v/>
       </c>
       <c r="D65" s="9" t="str">
-        <f aca="false">IF(A65="","","Hola, "&amp;TRIM(A65)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B65="",""," (hasta "&amp;B65&amp;IF(B65=1," persona)"," personas)"))&amp;": "&amp;C65&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A65="","","Hola, "&amp;TRIM(A65)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B65="",""," (hasta "&amp;B65&amp;IF(B65=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E65" s="7"/>
@@ -1855,7 +1855,7 @@
         <v/>
       </c>
       <c r="D66" s="9" t="str">
-        <f aca="false">IF(A66="","","Hola, "&amp;TRIM(A66)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B66="",""," (hasta "&amp;B66&amp;IF(B66=1," persona)"," personas)"))&amp;": "&amp;C66&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A66="","","Hola, "&amp;TRIM(A66)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B66="",""," (hasta "&amp;B66&amp;IF(B66=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E66" s="7"/>
@@ -1874,7 +1874,7 @@
         <v/>
       </c>
       <c r="D67" s="9" t="str">
-        <f aca="false">IF(A67="","","Hola, "&amp;TRIM(A67)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B67="",""," (hasta "&amp;B67&amp;IF(B67=1," persona)"," personas)"))&amp;": "&amp;C67&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A67="","","Hola, "&amp;TRIM(A67)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B67="",""," (hasta "&amp;B67&amp;IF(B67=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E67" s="7"/>
@@ -1893,7 +1893,7 @@
         <v/>
       </c>
       <c r="D68" s="9" t="str">
-        <f aca="false">IF(A68="","","Hola, "&amp;TRIM(A68)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B68="",""," (hasta "&amp;B68&amp;IF(B68=1," persona)"," personas)"))&amp;": "&amp;C68&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A68="","","Hola, "&amp;TRIM(A68)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B68="",""," (hasta "&amp;B68&amp;IF(B68=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E68" s="7"/>
@@ -1912,7 +1912,7 @@
         <v/>
       </c>
       <c r="D69" s="9" t="str">
-        <f aca="false">IF(A69="","","Hola, "&amp;TRIM(A69)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B69="",""," (hasta "&amp;B69&amp;IF(B69=1," persona)"," personas)"))&amp;": "&amp;C69&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A69="","","Hola, "&amp;TRIM(A69)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B69="",""," (hasta "&amp;B69&amp;IF(B69=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E69" s="7"/>
@@ -1931,7 +1931,7 @@
         <v/>
       </c>
       <c r="D70" s="9" t="str">
-        <f aca="false">IF(A70="","","Hola, "&amp;TRIM(A70)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B70="",""," (hasta "&amp;B70&amp;IF(B70=1," persona)"," personas)"))&amp;": "&amp;C70&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A70="","","Hola, "&amp;TRIM(A70)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B70="",""," (hasta "&amp;B70&amp;IF(B70=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E70" s="7"/>
@@ -1950,7 +1950,7 @@
         <v/>
       </c>
       <c r="D71" s="9" t="str">
-        <f aca="false">IF(A71="","","Hola, "&amp;TRIM(A71)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B71="",""," (hasta "&amp;B71&amp;IF(B71=1," persona)"," personas)"))&amp;": "&amp;C71&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A71="","","Hola, "&amp;TRIM(A71)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B71="",""," (hasta "&amp;B71&amp;IF(B71=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E71" s="7"/>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D72" s="9" t="str">
-        <f aca="false">IF(A72="","","Hola, "&amp;TRIM(A72)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B72="",""," (hasta "&amp;B72&amp;IF(B72=1," persona)"," personas)"))&amp;": "&amp;C72&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A72="","","Hola, "&amp;TRIM(A72)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B72="",""," (hasta "&amp;B72&amp;IF(B72=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E72" s="7"/>
@@ -1988,7 +1988,7 @@
         <v/>
       </c>
       <c r="D73" s="9" t="str">
-        <f aca="false">IF(A73="","","Hola, "&amp;TRIM(A73)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B73="",""," (hasta "&amp;B73&amp;IF(B73=1," persona)"," personas)"))&amp;": "&amp;C73&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A73="","","Hola, "&amp;TRIM(A73)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B73="",""," (hasta "&amp;B73&amp;IF(B73=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E73" s="7"/>
@@ -2007,7 +2007,7 @@
         <v/>
       </c>
       <c r="D74" s="9" t="str">
-        <f aca="false">IF(A74="","","Hola, "&amp;TRIM(A74)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B74="",""," (hasta "&amp;B74&amp;IF(B74=1," persona)"," personas)"))&amp;": "&amp;C74&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A74="","","Hola, "&amp;TRIM(A74)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B74="",""," (hasta "&amp;B74&amp;IF(B74=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E74" s="7"/>
@@ -2026,7 +2026,7 @@
         <v/>
       </c>
       <c r="D75" s="9" t="str">
-        <f aca="false">IF(A75="","","Hola, "&amp;TRIM(A75)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B75="",""," (hasta "&amp;B75&amp;IF(B75=1," persona)"," personas)"))&amp;": "&amp;C75&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A75="","","Hola, "&amp;TRIM(A75)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B75="",""," (hasta "&amp;B75&amp;IF(B75=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E75" s="7"/>
@@ -2045,7 +2045,7 @@
         <v/>
       </c>
       <c r="D76" s="9" t="str">
-        <f aca="false">IF(A76="","","Hola, "&amp;TRIM(A76)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B76="",""," (hasta "&amp;B76&amp;IF(B76=1," persona)"," personas)"))&amp;": "&amp;C76&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A76="","","Hola, "&amp;TRIM(A76)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B76="",""," (hasta "&amp;B76&amp;IF(B76=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E76" s="7"/>
@@ -2064,7 +2064,7 @@
         <v/>
       </c>
       <c r="D77" s="9" t="str">
-        <f aca="false">IF(A77="","","Hola, "&amp;TRIM(A77)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B77="",""," (hasta "&amp;B77&amp;IF(B77=1," persona)"," personas)"))&amp;": "&amp;C77&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A77="","","Hola, "&amp;TRIM(A77)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B77="",""," (hasta "&amp;B77&amp;IF(B77=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E77" s="7"/>
@@ -2083,7 +2083,7 @@
         <v/>
       </c>
       <c r="D78" s="9" t="str">
-        <f aca="false">IF(A78="","","Hola, "&amp;TRIM(A78)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B78="",""," (hasta "&amp;B78&amp;IF(B78=1," persona)"," personas)"))&amp;": "&amp;C78&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A78="","","Hola, "&amp;TRIM(A78)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B78="",""," (hasta "&amp;B78&amp;IF(B78=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E78" s="7"/>
@@ -2102,7 +2102,7 @@
         <v/>
       </c>
       <c r="D79" s="9" t="str">
-        <f aca="false">IF(A79="","","Hola, "&amp;TRIM(A79)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B79="",""," (hasta "&amp;B79&amp;IF(B79=1," persona)"," personas)"))&amp;": "&amp;C79&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A79="","","Hola, "&amp;TRIM(A79)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B79="",""," (hasta "&amp;B79&amp;IF(B79=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E79" s="7"/>
@@ -2121,7 +2121,7 @@
         <v/>
       </c>
       <c r="D80" s="9" t="str">
-        <f aca="false">IF(A80="","","Hola, "&amp;TRIM(A80)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B80="",""," (hasta "&amp;B80&amp;IF(B80=1," persona)"," personas)"))&amp;": "&amp;C80&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A80="","","Hola, "&amp;TRIM(A80)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B80="",""," (hasta "&amp;B80&amp;IF(B80=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E80" s="7"/>
@@ -2140,7 +2140,7 @@
         <v/>
       </c>
       <c r="D81" s="9" t="str">
-        <f aca="false">IF(A81="","","Hola, "&amp;TRIM(A81)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B81="",""," (hasta "&amp;B81&amp;IF(B81=1," persona)"," personas)"))&amp;": "&amp;C81&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A81="","","Hola, "&amp;TRIM(A81)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B81="",""," (hasta "&amp;B81&amp;IF(B81=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E81" s="7"/>
@@ -2159,7 +2159,7 @@
         <v/>
       </c>
       <c r="D82" s="9" t="str">
-        <f aca="false">IF(A82="","","Hola, "&amp;TRIM(A82)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B82="",""," (hasta "&amp;B82&amp;IF(B82=1," persona)"," personas)"))&amp;": "&amp;C82&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A82="","","Hola, "&amp;TRIM(A82)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B82="",""," (hasta "&amp;B82&amp;IF(B82=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E82" s="7"/>
@@ -2178,7 +2178,7 @@
         <v/>
       </c>
       <c r="D83" s="9" t="str">
-        <f aca="false">IF(A83="","","Hola, "&amp;TRIM(A83)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B83="",""," (hasta "&amp;B83&amp;IF(B83=1," persona)"," personas)"))&amp;": "&amp;C83&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A83="","","Hola, "&amp;TRIM(A83)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B83="",""," (hasta "&amp;B83&amp;IF(B83=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E83" s="7"/>
@@ -2197,7 +2197,7 @@
         <v/>
       </c>
       <c r="D84" s="9" t="str">
-        <f aca="false">IF(A84="","","Hola, "&amp;TRIM(A84)&amp;". Con mucha alegría los invitamos a la boda de Cristian y Daniela, el miércoles 23 de diciembre de 2026. Aquí está su invitación personalizada"&amp;IF(B84="",""," (hasta "&amp;B84&amp;IF(B84=1," persona)"," personas)"))&amp;": "&amp;C84&amp;"  Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026. ¡Los esperamos con mucho cariño!")</f>
+        <f aca="false">IF(A84="","","Hola, "&amp;TRIM(A84)&amp;" 🤍 Con mucha alegría los invitamos a la boda de Cristian y Daniela 💍 "&amp;"Será el miércoles 23 de diciembre de 2026 a las 10:00 a. m., en un ambiente campestre 🌿 "&amp;"En el enlace que les acabamos de enviar está su invitación personalizada"&amp;IF(B84="",""," (hasta "&amp;B84&amp;IF(B84=1," persona)"," personas)"))&amp;" ✨ "&amp;"Por favor confirmen su asistencia antes del martes 1 de diciembre de 2026 📅 "&amp;"¡Los esperamos con mucho cariño! 🤍")</f>
         <v/>
       </c>
       <c r="E84" s="7"/>
@@ -2259,7 +2259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="n">
         <v>1</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="n">
         <v>4</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="n">
         <v>5</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="n">
         <v>8</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="n">
         <v>9</v>
       </c>
